--- a/Results/Hydrogen/hydrogen climate change image breakdown results.xlsx
+++ b/Results/Hydrogen/hydrogen climate change image breakdown results.xlsx
@@ -576,70 +576,70 @@
         <v>10.22165460521644</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0227002191238591</v>
+        <v>0.02270021912385906</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05308205105750137</v>
+        <v>0.05308205105750122</v>
       </c>
       <c r="G2" t="n">
-        <v>3.98527207456663e-05</v>
+        <v>3.985272074566633e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001115255165955142</v>
+        <v>0.001115255165955134</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002205175860169976</v>
+        <v>0.0002205175860169983</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002128622578102894</v>
+        <v>0.002128622578102899</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003900280690608188</v>
+        <v>0.003900280690608178</v>
       </c>
       <c r="L2" t="n">
-        <v>3.270949890655773e-05</v>
+        <v>3.27094989065577e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001299537423176717</v>
+        <v>0.0001299537423176716</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004199541260297481</v>
+        <v>0.004199541260297484</v>
       </c>
       <c r="O2" t="n">
-        <v>3.143082184608752e-05</v>
+        <v>3.143082184608704e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.77867574631262e-07</v>
+        <v>4.778675746312623e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.853163234309913e-05</v>
+        <v>5.853163234309905e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>5.265839532949526e-07</v>
+        <v>5.265839532949482e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>2.591884726465943e-06</v>
+        <v>2.591884726465939e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008443316304906568</v>
+        <v>0.0008443316304906541</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002925298942202898</v>
+        <v>0.002925298942202718</v>
       </c>
       <c r="V2" t="n">
         <v>0.004490075408785341</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002850715184561772</v>
+        <v>0.0002850715184561761</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.866790528392906</v>
+        <v>-0.8667905283929052</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.067067849168917</v>
+        <v>2.067067849168916</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.925189944725737</v>
+        <v>8.925189944725739</v>
       </c>
     </row>
     <row r="3">
@@ -657,73 +657,73 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10.22548817902285</v>
+        <v>10.22548817902284</v>
       </c>
       <c r="E3" t="n">
         <v>0.02048024079670932</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05003569596162554</v>
+        <v>0.05003569596162553</v>
       </c>
       <c r="G3" t="n">
-        <v>3.915212087094495e-05</v>
+        <v>3.915212087094496e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001100894084210146</v>
+        <v>0.001100894084210139</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002162432485330635</v>
+        <v>0.000216243248533064</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002026845154859619</v>
+        <v>0.002026845154859623</v>
       </c>
       <c r="K3" t="n">
         <v>0.003701499362393962</v>
       </c>
       <c r="L3" t="n">
-        <v>3.227306198337603e-05</v>
+        <v>3.227306198337605e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001225554608451963</v>
+        <v>0.0001225554608451964</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004094740998576131</v>
+        <v>0.004094740998576134</v>
       </c>
       <c r="O3" t="n">
-        <v>2.975282940735076e-05</v>
+        <v>2.975282940735109e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.736527799420422e-07</v>
+        <v>4.736527799420413e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.822260296368421e-05</v>
+        <v>5.82226029636842e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.047564178185933e-07</v>
+        <v>5.047564178185946e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.388163631993297e-06</v>
+        <v>2.3881636319933e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008018113496355745</v>
+        <v>0.000801811349635577</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002814409846142652</v>
+        <v>0.002814409846140893</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004481593192334517</v>
+        <v>0.004481593192334515</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002719728644802263</v>
+        <v>0.0002719728644802286</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8311087011517542</v>
+        <v>-0.8311087011517551</v>
       </c>
       <c r="Y3" t="n">
         <v>2.041095664701162</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.925189945965037</v>
+        <v>8.925189945965039</v>
       </c>
     </row>
     <row r="4">
@@ -741,73 +741,73 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.2225876411482</v>
+        <v>10.22258764114819</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0207297399899222</v>
+        <v>0.02072973998992222</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04889485464727755</v>
+        <v>0.04889485464727761</v>
       </c>
       <c r="G4" t="n">
-        <v>3.885189094558879e-05</v>
+        <v>3.885189094558883e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00108704113031509</v>
+        <v>0.001087041130315091</v>
       </c>
       <c r="I4" t="n">
         <v>0.0002137106605180963</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001949002174831591</v>
+        <v>0.00194900217483161</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003467377085039129</v>
+        <v>0.003467377085039127</v>
       </c>
       <c r="L4" t="n">
         <v>3.196076362873073e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001177395391075737</v>
+        <v>0.0001177395391075764</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003964355585938002</v>
+        <v>0.003964355585938006</v>
       </c>
       <c r="O4" t="n">
-        <v>2.80791072638096e-05</v>
+        <v>2.807910726380981e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.728200165923967e-07</v>
+        <v>4.72820016592397e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.783000336517309e-05</v>
+        <v>5.783000336517311e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.31242584317881e-07</v>
+        <v>4.312425843178825e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.411619078280515e-06</v>
+        <v>2.41161907828052e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007947470088704113</v>
+        <v>0.0007947470088704096</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002756151472437525</v>
+        <v>0.0027561514724341</v>
       </c>
       <c r="V4" t="n">
         <v>0.004465977913432203</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002671569679113352</v>
+        <v>0.0002671569679113319</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8130614307819766</v>
+        <v>-0.8130614307819781</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.02159123376064</v>
+        <v>2.021591233760639</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.92518994654705</v>
+        <v>8.925189946547054</v>
       </c>
     </row>
     <row r="5">
@@ -825,70 +825,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.26755288259755</v>
+        <v>10.26755288259756</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02236734438006396</v>
+        <v>0.02236734438006398</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04847054725608914</v>
+        <v>0.04847054725608909</v>
       </c>
       <c r="G5" t="n">
-        <v>3.894127927433724e-05</v>
+        <v>3.894127927433888e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001068697363285019</v>
+        <v>0.001068697363285021</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002125588825709756</v>
+        <v>0.0002125588825709768</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001867585408417362</v>
+        <v>0.001867585408417363</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003357730581222934</v>
+        <v>0.003357730581222936</v>
       </c>
       <c r="L5" t="n">
-        <v>3.174583167467178e-05</v>
+        <v>3.174583167467175e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001125487399986646</v>
+        <v>0.0001125487399986647</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003895325081054397</v>
+        <v>0.003895325081054394</v>
       </c>
       <c r="O5" t="n">
-        <v>2.737288857804448e-05</v>
+        <v>2.73728885780491e-05</v>
       </c>
       <c r="P5" t="n">
         <v>4.757667560146273e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.75591343558614e-05</v>
+        <v>5.755913435586139e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.950457905261766e-07</v>
+        <v>3.95045790526174e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.529356284239831e-06</v>
+        <v>2.529356284239832e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0007959169810263862</v>
+        <v>0.0007959169810263897</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002680810707825065</v>
+        <v>0.002680810707827695</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004460514450454931</v>
+        <v>0.004460514450454932</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000266634920406638</v>
+        <v>0.0002666349204066353</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7577854763497635</v>
+        <v>-0.7577854763497598</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.010433176106735</v>
+        <v>2.010433176106734</v>
       </c>
       <c r="Z5" t="n">
         <v>8.925189948785453</v>
@@ -909,73 +909,73 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.6514373692406</v>
+        <v>10.65143736924059</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01333464514315236</v>
+        <v>0.01333464514315235</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02974977801199184</v>
+        <v>0.02974977801199182</v>
       </c>
       <c r="G6" t="n">
-        <v>3.557291654807427e-05</v>
+        <v>3.55729165480742e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009450929731583709</v>
+        <v>0.0009450929731583679</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001884763489467235</v>
+        <v>0.000188476348946723</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001098273478484795</v>
+        <v>0.001098273478484796</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002858426921536694</v>
+        <v>0.002858426921536689</v>
       </c>
       <c r="L6" t="n">
-        <v>2.897726556060289e-05</v>
+        <v>2.897726556060291e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>6.900073509824883e-05</v>
+        <v>6.900073509824867e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003379888739612392</v>
+        <v>0.003379888739612387</v>
       </c>
       <c r="O6" t="n">
-        <v>2.066869182407517e-05</v>
+        <v>2.066869182407516e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.612147143650066e-07</v>
+        <v>4.612147143650063e-07</v>
       </c>
       <c r="Q6" t="n">
         <v>5.586993600659039e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.640600962990073e-07</v>
+        <v>2.640600962990049e-07</v>
       </c>
       <c r="S6" t="n">
         <v>1.633036342628584e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005229314890986627</v>
+        <v>0.0005229314890986636</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001774626686367572</v>
+        <v>0.001774626686364299</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004450404181114826</v>
+        <v>0.004450404181114825</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001877795718651598</v>
+        <v>0.0001877795718651599</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2520044213705994</v>
+        <v>-0.2520044213705991</v>
       </c>
       <c r="Y6" t="n">
         <v>1.91954904999956</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.925189969210114</v>
+        <v>8.925189969210111</v>
       </c>
     </row>
     <row r="7">
@@ -993,73 +993,73 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.8715170791576</v>
+        <v>10.87151707915761</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008476293576814613</v>
+        <v>0.008476293576814649</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0170515891242242</v>
+        <v>0.01705158912422423</v>
       </c>
       <c r="G7" t="n">
-        <v>3.286973274047282e-05</v>
+        <v>3.286973274047278e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008656833507891925</v>
+        <v>0.0008656833507891894</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001697664162161625</v>
+        <v>0.0001697664162161634</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0004750226343078688</v>
+        <v>0.0004750226343078736</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002341389141919825</v>
+        <v>0.002341389141919828</v>
       </c>
       <c r="L7" t="n">
         <v>2.67328876904949e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.347186743102315e-05</v>
+        <v>3.34718674310232e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002873085815783586</v>
+        <v>0.002873085815783579</v>
       </c>
       <c r="O7" t="n">
-        <v>1.360686688872267e-05</v>
+        <v>1.360686688872258e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.537472227772393e-07</v>
+        <v>4.537472227772391e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.422655037948617e-05</v>
+        <v>5.422655037948621e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.643427683818886e-07</v>
+        <v>1.643427683818888e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.141030670890406e-06</v>
+        <v>1.141030670890407e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0003546259244363513</v>
+        <v>0.0003546259244363526</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001149123231431673</v>
+        <v>0.001149123231433568</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004418543262183571</v>
+        <v>0.00441854326218357</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001319035125292639</v>
+        <v>0.0001319035125292626</v>
       </c>
       <c r="X7" t="n">
-        <v>0.08229348847880145</v>
+        <v>0.0822934884787998</v>
       </c>
       <c r="Y7" t="n">
         <v>1.825563915278472</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.925189982383902</v>
+        <v>8.925189982383905</v>
       </c>
     </row>
     <row r="8">
@@ -1080,70 +1080,70 @@
         <v>10.89587323286687</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007219537176829485</v>
+        <v>0.007219537176829468</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01420196909820722</v>
+        <v>0.01420196909820713</v>
       </c>
       <c r="G8" t="n">
-        <v>3.215985614680546e-05</v>
+        <v>3.215985614680547e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008513649928122562</v>
+        <v>0.0008513649928122536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001650617005982354</v>
+        <v>0.0001650617005982347</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003447053161818797</v>
+        <v>0.0003447053161818757</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002199999116180165</v>
+        <v>0.002199999116180163</v>
       </c>
       <c r="L8" t="n">
-        <v>2.612881040763221e-05</v>
+        <v>2.61288104076322e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.779359026718356e-05</v>
+        <v>2.779359026718348e-05</v>
       </c>
       <c r="N8" t="n">
         <v>0.002723733185990789</v>
       </c>
       <c r="O8" t="n">
-        <v>1.124443541159927e-05</v>
+        <v>1.124443541159945e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.506466716934946e-07</v>
+        <v>4.50646671693495e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.375352705890049e-05</v>
+        <v>5.375352705890047e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.243787894018886e-07</v>
+        <v>1.243787894018891e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.018545863442952e-06</v>
+        <v>1.01854586344295e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0003156720499268721</v>
+        <v>0.0003156720499268735</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001012864793603529</v>
+        <v>0.001012864793600341</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004406278734951296</v>
+        <v>0.004406278734951295</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0001182083785511757</v>
+        <v>0.0001182083785511742</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1445976743690113</v>
+        <v>0.1445976743690111</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.792373505488351</v>
+        <v>1.792373505488352</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.925189984675054</v>
+        <v>8.925189984675061</v>
       </c>
     </row>
     <row r="9">
@@ -1164,67 +1164,67 @@
         <v>10.31952667573078</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01858743815737441</v>
+        <v>0.01858743815737431</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0447104051424459</v>
+        <v>0.0447104051424458</v>
       </c>
       <c r="G9" t="n">
-        <v>3.812355357862534e-05</v>
+        <v>3.812355357862539e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001075097487370484</v>
+        <v>0.001075097487370465</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002090648855695435</v>
+        <v>0.0002090648855695434</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001782601022928903</v>
+        <v>0.001782601022928907</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00337473482345665</v>
+        <v>0.00337473482345664</v>
       </c>
       <c r="L9" t="n">
-        <v>3.141484724925026e-05</v>
+        <v>3.141484724925019e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001102306969218482</v>
+        <v>0.000110230696921848</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00385167453294824</v>
+        <v>0.003851674532948233</v>
       </c>
       <c r="O9" t="n">
-        <v>2.721404332568385e-05</v>
+        <v>2.721404332567761e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.705482744173573e-07</v>
+        <v>4.705482744173575e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.75949939110192e-05</v>
+        <v>5.759499391101915e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.868064366903064e-07</v>
+        <v>4.868064366903045e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.199018546220208e-06</v>
+        <v>2.1990185462202e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0007294182168443207</v>
+        <v>0.0007294182168443189</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002543323647062126</v>
+        <v>0.002543323647065098</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004471286981995341</v>
+        <v>0.004471286981995339</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002502874278185769</v>
+        <v>0.0002502874278185761</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.689023497081052</v>
+        <v>-0.68902349708105</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.001507154410185</v>
+        <v>2.001507154410184</v>
       </c>
       <c r="Z9" t="n">
         <v>8.925189951567585</v>
@@ -1245,73 +1245,73 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.66212344211596</v>
+        <v>10.66212344211597</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01292388667267728</v>
+        <v>0.0129238866726773</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02850690054408216</v>
+        <v>0.02850690054408208</v>
       </c>
       <c r="G10" t="n">
-        <v>3.502639669367301e-05</v>
+        <v>3.502639669367293e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.000986536025872716</v>
+        <v>0.0009865360258727194</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001863716461798051</v>
+        <v>0.0001863716461798045</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0009951979209537555</v>
+        <v>0.0009951979209537512</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002784481607635456</v>
+        <v>0.002784481607635466</v>
       </c>
       <c r="L10" t="n">
-        <v>2.875054490214754e-05</v>
+        <v>2.875054490214755e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>6.974058037107731e-05</v>
+        <v>6.974058037107727e-05</v>
       </c>
       <c r="N10" t="n">
         <v>0.003339163850790112</v>
       </c>
       <c r="O10" t="n">
-        <v>1.984567148451326e-05</v>
+        <v>1.984567148451365e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>4.618975724849155e-07</v>
+        <v>4.618975724849149e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.56330701164787e-05</v>
+        <v>5.563307011647867e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>2.90239477316666e-07</v>
+        <v>2.90239477316667e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.59992662812225e-06</v>
+        <v>1.599926628122253e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0005104313945013854</v>
+        <v>0.0005104313945013874</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001717210647423383</v>
+        <v>0.001717210647423031</v>
       </c>
       <c r="V10" t="n">
-        <v>0.004441700502863798</v>
+        <v>0.004441700502863796</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0001817943621944903</v>
+        <v>0.0001817943621944889</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2258318468226158</v>
+        <v>-0.2258318468226167</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.905980295255848</v>
+        <v>1.905980295255847</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.925189970180311</v>
+        <v>8.925189970180316</v>
       </c>
     </row>
     <row r="11">
@@ -1332,70 +1332,70 @@
         <v>10.88331703981609</v>
       </c>
       <c r="E11" t="n">
-        <v>0.009550451786631144</v>
+        <v>0.009550451786631043</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0188337655649733</v>
+        <v>0.01883376556497357</v>
       </c>
       <c r="G11" t="n">
-        <v>3.341766394406026e-05</v>
+        <v>3.341766394405991e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0008721373607343268</v>
+        <v>0.0008721373607343247</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001729786393783531</v>
+        <v>0.0001729786393783528</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0005556284265742913</v>
+        <v>0.0005556284265742866</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002481445120361053</v>
+        <v>0.00248144512036106</v>
       </c>
       <c r="L11" t="n">
-        <v>2.713021612975457e-05</v>
+        <v>2.713021612975466e-05</v>
       </c>
       <c r="M11" t="n">
         <v>3.983208759955751e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.002986855562072279</v>
+        <v>0.002986855562072295</v>
       </c>
       <c r="O11" t="n">
-        <v>1.545148555675502e-05</v>
+        <v>1.54514855567567e-05</v>
       </c>
       <c r="P11" t="n">
         <v>4.568847731624876e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.451835567921246e-05</v>
+        <v>5.451835567921226e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.280608705545545e-07</v>
+        <v>2.280608705545531e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.233512570689246e-06</v>
+        <v>1.233512570689243e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0003781730969176309</v>
+        <v>0.0003781730969176389</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001219540421548022</v>
+        <v>0.001219540421550201</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004427310572784781</v>
+        <v>0.004427310572784784</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0001407490507696166</v>
+        <v>0.0001407490507696155</v>
       </c>
       <c r="X11" t="n">
-        <v>0.06003381943600732</v>
+        <v>0.06003381943600799</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.856301934746677</v>
+        <v>1.856301934746672</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.925189981763534</v>
+        <v>8.925189981763536</v>
       </c>
     </row>
   </sheetData>
@@ -1567,76 +1567,76 @@
         <v>4.392127753066371</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04189358546773075</v>
+        <v>0.0418935854677307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0226976183020887</v>
+        <v>0.02269761830208868</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05307596931206727</v>
+        <v>0.05307596931206724</v>
       </c>
       <c r="H2" t="n">
-        <v>3.98527207456663e-05</v>
+        <v>3.985272074566633e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001115255165955142</v>
+        <v>0.001115255165955134</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002205175860169976</v>
+        <v>0.0002205175860169983</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002128622578102894</v>
+        <v>0.002128622578102899</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006329209035978133</v>
+        <v>0.0006329209035978127</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003900280690608188</v>
+        <v>0.003900280690608178</v>
       </c>
       <c r="N2" t="n">
-        <v>3.270949890655773e-05</v>
+        <v>3.27094989065577e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001299537423176717</v>
+        <v>0.0001299537423176716</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004199541260297481</v>
+        <v>0.004199541260297484</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.143082184608752e-05</v>
+        <v>3.143082184608704e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>4.77867574631262e-07</v>
+        <v>4.778675746312623e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>5.853163234309913e-05</v>
+        <v>5.853163234309905e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>5.265839532949526e-07</v>
+        <v>5.265839532949482e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>2.591587767648664e-06</v>
+        <v>2.591587767648663e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.000844234893270896</v>
+        <v>0.0008442348932708939</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002924963783271969</v>
+        <v>0.002924963783271769</v>
       </c>
       <c r="X2" t="n">
         <v>0.004490075408785341</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002850715184561772</v>
+        <v>0.0002850715184561761</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.394392471734727</v>
+        <v>-0.3943924717347276</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.034710244953607</v>
+        <v>2.034710244953606</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.613105248521787</v>
+        <v>2.613105248521789</v>
       </c>
     </row>
     <row r="3">
@@ -1654,79 +1654,79 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.375174408837591</v>
+        <v>4.375174408837592</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04016563657124723</v>
+        <v>0.04016563657124726</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02047789432349527</v>
+        <v>0.02047789432349526</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05002996324483362</v>
+        <v>0.05002996324483363</v>
       </c>
       <c r="H3" t="n">
-        <v>3.915212087094495e-05</v>
+        <v>3.915212087094496e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001100894084210146</v>
+        <v>0.001100894084210139</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002162432485330635</v>
+        <v>0.000216243248533064</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002026845154859619</v>
+        <v>0.002026845154859623</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006132475543693551</v>
+        <v>0.0006132475543693558</v>
       </c>
       <c r="M3" t="n">
         <v>0.003701499362393962</v>
       </c>
       <c r="N3" t="n">
-        <v>3.227306198337603e-05</v>
+        <v>3.227306198337605e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001225554608451963</v>
+        <v>0.0001225554608451964</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004094740998576131</v>
+        <v>0.004094740998576134</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.975282940735076e-05</v>
+        <v>2.975282940735109e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.736527799420422e-07</v>
+        <v>4.736527799420413e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>5.822260296368421e-05</v>
+        <v>5.82226029636842e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.047564178185933e-07</v>
+        <v>5.047564178185946e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>2.387890014019328e-06</v>
+        <v>2.387890014019326e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008017194840724038</v>
+        <v>0.0008017194840724077</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002814087392056398</v>
+        <v>0.002814087392055218</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004481593192334517</v>
+        <v>0.004481593192334515</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002719728644802263</v>
+        <v>0.0002719728644802286</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.378157125845865</v>
+        <v>-0.3781571258458649</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.009144625594952</v>
+        <v>2.009144625594951</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.61310524923776</v>
+        <v>2.613105249237762</v>
       </c>
     </row>
     <row r="4">
@@ -1744,79 +1744,79 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.36184510576022</v>
+        <v>4.361845105760217</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0392649692746448</v>
+        <v>0.03926496927464466</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02072736493095177</v>
+        <v>0.02072736493095178</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04888925263957296</v>
+        <v>0.04888925263957306</v>
       </c>
       <c r="H4" t="n">
-        <v>3.885189094558879e-05</v>
+        <v>3.885189094558883e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00108704113031509</v>
+        <v>0.001087041130315091</v>
       </c>
       <c r="J4" t="n">
         <v>0.0002137106605180963</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001949002174831591</v>
+        <v>0.00194900217483161</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006154246831809813</v>
+        <v>0.0006154246831809819</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003467377085039129</v>
+        <v>0.003467377085039127</v>
       </c>
       <c r="N4" t="n">
         <v>3.196076362873073e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001177395391075737</v>
+        <v>0.0001177395391075764</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003964355585938002</v>
+        <v>0.003964355585938006</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.80791072638096e-05</v>
+        <v>2.807910726380981e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.728200165923967e-07</v>
+        <v>4.72820016592397e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.783000336517309e-05</v>
+        <v>5.783000336517311e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.31242584317881e-07</v>
+        <v>4.312425843178825e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.411342772956482e-06</v>
+        <v>2.411342772956489e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007946559526867102</v>
+        <v>0.0007946559526867072</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002755835693160872</v>
+        <v>0.002755835693160801</v>
       </c>
       <c r="X4" t="n">
         <v>0.004465977913432203</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002671569679113352</v>
+        <v>0.0002671569679113319</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.3699455599183974</v>
+        <v>-0.3699455599183982</v>
       </c>
       <c r="AA4" t="n">
         <v>1.98994551441308</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.613105249863669</v>
+        <v>2.613105249863667</v>
       </c>
     </row>
     <row r="5">
@@ -1834,79 +1834,79 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.374186435089804</v>
+        <v>4.374186435089807</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03658428299571905</v>
+        <v>0.03658428299571894</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02236478169659856</v>
+        <v>0.02236478169659855</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04846499386236024</v>
+        <v>0.0484649938623602</v>
       </c>
       <c r="H5" t="n">
-        <v>3.894127927433724e-05</v>
+        <v>3.894127927433888e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001068697363285019</v>
+        <v>0.001068697363285021</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002125588825709756</v>
+        <v>0.0002125588825709768</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001867585408417362</v>
+        <v>0.001867585408417363</v>
       </c>
       <c r="L5" t="n">
         <v>0.0006228824626762678</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003357730581222934</v>
+        <v>0.003357730581222936</v>
       </c>
       <c r="N5" t="n">
-        <v>3.174583167467178e-05</v>
+        <v>3.174583167467175e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001125487399986646</v>
+        <v>0.0001125487399986647</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003895325081054397</v>
+        <v>0.003895325081054394</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.737288857804448e-05</v>
+        <v>2.73728885780491e-05</v>
       </c>
       <c r="R5" t="n">
         <v>4.757667560146273e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>5.75591343558614e-05</v>
+        <v>5.755913435586139e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>3.950457905261766e-07</v>
+        <v>3.95045790526174e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.529066489465021e-06</v>
+        <v>2.529066489465019e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0007958257907960013</v>
+        <v>0.0007958257907960045</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002680503560532197</v>
+        <v>0.002680503560532484</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004460514450454931</v>
+        <v>0.004460514450454932</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000266634920406638</v>
+        <v>0.0002666349204066353</v>
       </c>
       <c r="Z5" t="n">
         <v>-0.3447948232849061</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.9789621235044</v>
+        <v>1.978962123504397</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.613105250061298</v>
+        <v>2.613105250061303</v>
       </c>
     </row>
     <row r="6">
@@ -1924,79 +1924,79 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.459399664695814</v>
+        <v>4.459399664695813</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01226195282216763</v>
+        <v>0.01226195282216765</v>
       </c>
       <c r="F6" t="n">
         <v>0.0133331173589843</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02974636950435164</v>
+        <v>0.02974636950435157</v>
       </c>
       <c r="H6" t="n">
-        <v>3.557291654807427e-05</v>
+        <v>3.55729165480742e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009450929731583709</v>
+        <v>0.0009450929731583679</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001884763489467235</v>
+        <v>0.000188476348946723</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001098273478484795</v>
+        <v>0.001098273478484796</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000497024399145118</v>
+        <v>0.0004970243991451181</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002858426921536694</v>
+        <v>0.002858426921536689</v>
       </c>
       <c r="N6" t="n">
-        <v>2.897726556060289e-05</v>
+        <v>2.897726556060291e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.900073509824883e-05</v>
+        <v>6.900073509824867e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003379888739612392</v>
+        <v>0.003379888739612387</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.066869182407517e-05</v>
+        <v>2.066869182407516e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.612147143650066e-07</v>
+        <v>4.612147143650063e-07</v>
       </c>
       <c r="S6" t="n">
         <v>5.586993600659039e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.640600962990073e-07</v>
+        <v>2.640600962990049e-07</v>
       </c>
       <c r="U6" t="n">
         <v>1.632849241506407e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005228715755095536</v>
+        <v>0.0005228715755095539</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001774423362880268</v>
+        <v>0.001774423362876758</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004450404181114826</v>
+        <v>0.004450404181114825</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001877795718651598</v>
+        <v>0.0001877795718651599</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1146628203433468</v>
+        <v>-0.1146628203433469</v>
       </c>
       <c r="AA6" t="n">
         <v>1.889500685376826</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.613105250755487</v>
+        <v>2.61310525075549</v>
       </c>
     </row>
     <row r="7">
@@ -2014,73 +2014,73 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.482576310348652</v>
+        <v>4.482576310348654</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.003850303329638003</v>
+        <v>-0.003850303329637953</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008475322426327196</v>
+        <v>0.008475322426327203</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01704963548034206</v>
+        <v>0.01704963548034209</v>
       </c>
       <c r="H7" t="n">
-        <v>3.286973274047282e-05</v>
+        <v>3.286973274047278e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008656833507891925</v>
+        <v>0.0008656833507891894</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001697664162161625</v>
+        <v>0.0001697664162161634</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004750226343078688</v>
+        <v>0.0004750226343078736</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004241826505483298</v>
+        <v>0.0004241826505483293</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002341389141919825</v>
+        <v>0.002341389141919828</v>
       </c>
       <c r="N7" t="n">
         <v>2.67328876904949e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>3.347186743102315e-05</v>
+        <v>3.34718674310232e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002873085815783586</v>
+        <v>0.002873085815783579</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.360686688872267e-05</v>
+        <v>1.360686688872258e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.537472227772393e-07</v>
+        <v>4.537472227772391e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>5.422655037948617e-05</v>
+        <v>5.422655037948621e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.643427683818886e-07</v>
+        <v>1.643427683818888e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>1.140899940107879e-06</v>
+        <v>1.14089994010788e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0003545852940433305</v>
+        <v>0.0003545852940433337</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001148991573464401</v>
+        <v>0.001148991573466216</v>
       </c>
       <c r="X7" t="n">
-        <v>0.004418543262183571</v>
+        <v>0.00441854326218357</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001319035125292639</v>
+        <v>0.0001319035125292626</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03744380131726102</v>
+        <v>0.03744380131726049</v>
       </c>
       <c r="AA7" t="n">
         <v>1.796986781410281</v>
@@ -2107,76 +2107,76 @@
         <v>4.47044562428855</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.006885807988445753</v>
+        <v>-0.00688580798844578</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007218710016115334</v>
+        <v>0.007218710016115322</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01420034194253035</v>
+        <v>0.0142003419425303</v>
       </c>
       <c r="H8" t="n">
-        <v>3.215985614680546e-05</v>
+        <v>3.215985614680547e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008513649928122562</v>
+        <v>0.0008513649928122536</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001650617005982354</v>
+        <v>0.0001650617005982347</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003447053161818797</v>
+        <v>0.0003447053161818757</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004083815123908287</v>
+        <v>0.0004083815123908286</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002199999116180165</v>
+        <v>0.002199999116180163</v>
       </c>
       <c r="N8" t="n">
-        <v>2.612881040763221e-05</v>
+        <v>2.61288104076322e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.779359026718356e-05</v>
+        <v>2.779359026718348e-05</v>
       </c>
       <c r="P8" t="n">
         <v>0.002723733185990789</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.124443541159927e-05</v>
+        <v>1.124443541159945e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>4.506466716934946e-07</v>
+        <v>4.50646671693495e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>5.375352705890049e-05</v>
+        <v>5.375352705890047e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.243787894018886e-07</v>
+        <v>1.243787894018891e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>1.018429166055967e-06</v>
+        <v>1.018429166055965e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0003156358825782109</v>
+        <v>0.0003156358825782103</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00101274874711809</v>
+        <v>0.001012748747108069</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004406278734951296</v>
+        <v>0.004406278734951295</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001182083785511757</v>
+        <v>0.0001182083785511742</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.06579240581599574</v>
+        <v>0.06579240581599589</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.764315929865027</v>
+        <v>1.764315929865028</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.613105253396055</v>
+        <v>2.613105253396065</v>
       </c>
     </row>
     <row r="9">
@@ -2194,79 +2194,79 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.385517786176866</v>
+        <v>4.385517786176867</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0333146127788782</v>
+        <v>0.03331461277887807</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01858530854736704</v>
+        <v>0.01858530854736692</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04470528255775093</v>
+        <v>0.04470528255775085</v>
       </c>
       <c r="H9" t="n">
-        <v>3.812355357862534e-05</v>
+        <v>3.812355357862539e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001075097487370484</v>
+        <v>0.001075097487370465</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002090648855695435</v>
+        <v>0.0002090648855695434</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001782601022928903</v>
+        <v>0.001782601022928907</v>
       </c>
       <c r="L9" t="n">
         <v>0.0005845575295737893</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00337473482345665</v>
+        <v>0.00337473482345664</v>
       </c>
       <c r="N9" t="n">
-        <v>3.141484724925026e-05</v>
+        <v>3.141484724925019e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001102306969218482</v>
+        <v>0.000110230696921848</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00385167453294824</v>
+        <v>0.003851674532948233</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.721404332568385e-05</v>
+        <v>2.721404332567761e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.705482744173573e-07</v>
+        <v>4.705482744173575e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>5.75949939110192e-05</v>
+        <v>5.759499391101915e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.868064366903064e-07</v>
+        <v>4.868064366903045e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.198766599079202e-06</v>
+        <v>2.198766599079193e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007293346455462764</v>
+        <v>0.0007293346455462726</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002543032252011078</v>
+        <v>0.002543032252009852</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004471286981995341</v>
+        <v>0.004471286981995339</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002502874278185769</v>
+        <v>0.0002502874278185761</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.3135079020774936</v>
+        <v>-0.3135079020774932</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.970175828560115</v>
+        <v>1.970175828560114</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.613105249964732</v>
+        <v>2.613105249964736</v>
       </c>
     </row>
     <row r="10">
@@ -2284,76 +2284,76 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.45478862896174</v>
+        <v>4.454788628961736</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01102146013223346</v>
+        <v>0.01102146013223349</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01292240595015061</v>
+        <v>0.01292240595015064</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0285036344360707</v>
+        <v>0.02850363443607063</v>
       </c>
       <c r="H10" t="n">
-        <v>3.502639669367301e-05</v>
+        <v>3.502639669367293e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000986536025872716</v>
+        <v>0.0009865360258727194</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001863716461798051</v>
+        <v>0.0001863716461798045</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0009951979209537555</v>
+        <v>0.0009951979209537512</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0004917772836323489</v>
+        <v>0.0004917772836323487</v>
       </c>
       <c r="M10" t="n">
-        <v>0.002784481607635456</v>
+        <v>0.002784481607635466</v>
       </c>
       <c r="N10" t="n">
-        <v>2.875054490214754e-05</v>
+        <v>2.875054490214755e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>6.974058037107731e-05</v>
+        <v>6.974058037107727e-05</v>
       </c>
       <c r="P10" t="n">
         <v>0.003339163850790112</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.984567148451326e-05</v>
+        <v>1.984567148451365e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.618975724849155e-07</v>
+        <v>4.618975724849149e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>5.56330701164787e-05</v>
+        <v>5.563307011647867e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.90239477316666e-07</v>
+        <v>2.90239477316667e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>1.599743320464172e-06</v>
+        <v>1.599743320464173e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0005103729130798695</v>
+        <v>0.0005103729130798696</v>
       </c>
       <c r="W10" t="n">
-        <v>0.00171701390223728</v>
+        <v>0.001717013902235611</v>
       </c>
       <c r="X10" t="n">
-        <v>0.004441700502863798</v>
+        <v>0.004441700502863796</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0001817943621944903</v>
+        <v>0.0001817943621944889</v>
       </c>
       <c r="Z10" t="n">
         <v>-0.1027542149427105</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.876144334108826</v>
+        <v>1.876144334108823</v>
       </c>
       <c r="AB10" t="n">
         <v>2.613105251117792</v>
@@ -2374,79 +2374,79 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.50714325724325</v>
+        <v>4.507143257243242</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.002743333231033676</v>
+        <v>-0.002743333231033735</v>
       </c>
       <c r="F11" t="n">
-        <v>0.009549357567108932</v>
+        <v>0.009549357567108868</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01883160773260912</v>
+        <v>0.01883160773260916</v>
       </c>
       <c r="H11" t="n">
-        <v>3.341766394406026e-05</v>
+        <v>3.341766394405991e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0008721373607343268</v>
+        <v>0.0008721373607343247</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001729786393783531</v>
+        <v>0.0001729786393783528</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0005556284265742913</v>
+        <v>0.0005556284265742866</v>
       </c>
       <c r="L11" t="n">
         <v>0.0004342578576933488</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002481445120361053</v>
+        <v>0.00248144512036106</v>
       </c>
       <c r="N11" t="n">
-        <v>2.713021612975457e-05</v>
+        <v>2.713021612975466e-05</v>
       </c>
       <c r="O11" t="n">
         <v>3.983208759955751e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002986855562072279</v>
+        <v>0.002986855562072295</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.545148555675502e-05</v>
+        <v>1.54514855567567e-05</v>
       </c>
       <c r="R11" t="n">
         <v>4.568847731624876e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>5.451835567921246e-05</v>
+        <v>5.451835567921226e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.280608705545545e-07</v>
+        <v>2.280608705545531e-07</v>
       </c>
       <c r="U11" t="n">
-        <v>1.233371244020528e-06</v>
+        <v>1.233371244020523e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0003781297686652564</v>
+        <v>0.0003781297686652509</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001219400695703887</v>
+        <v>0.001219400695704257</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004427310572784781</v>
+        <v>0.004427310572784784</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0001407490507696166</v>
+        <v>0.0001407490507696155</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.02731558047702979</v>
+        <v>0.02731558047703016</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.827243632024395</v>
+        <v>1.827243632024381</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.613105251492607</v>
+        <v>2.613105251492612</v>
       </c>
     </row>
   </sheetData>
@@ -2540,31 +2540,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.419105682990746</v>
+        <v>2.419105682990749</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3237534701542786</v>
+        <v>0.323753470154279</v>
       </c>
       <c r="F2" t="n">
         <v>0.05218557395712024</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01622465499368875</v>
+        <v>0.01622465499368885</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1041155420134817</v>
+        <v>0.1041155420134807</v>
       </c>
       <c r="I2" t="n">
-        <v>4.813530845089292e-06</v>
+        <v>4.813530845089288e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001568054437510769</v>
+        <v>0.001568054437510767</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005432732615621398</v>
+        <v>0.005432732615620378</v>
       </c>
       <c r="L2" t="n">
-        <v>1.915820885133452</v>
+        <v>1.915820885133451</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2585,31 +2585,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.17600132338278</v>
+        <v>2.176001323382777</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3100380369309446</v>
+        <v>0.3100380369309442</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03909404359035792</v>
+        <v>0.03909404359035786</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01599769206182827</v>
+        <v>0.01599769206182814</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1035766291563601</v>
+        <v>0.1035766291563592</v>
       </c>
       <c r="I3" t="n">
-        <v>4.435189261443129e-06</v>
+        <v>4.435189261443128e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00148908769900274</v>
+        <v>0.001489087699002744</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005226794412109219</v>
+        <v>0.005226794412108399</v>
       </c>
       <c r="L3" t="n">
-        <v>1.700574586283913</v>
+        <v>1.70057458628391</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -2630,28 +2630,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.971271592803706</v>
+        <v>1.971271592803703</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3026318292417142</v>
+        <v>0.3026318292417149</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0462305739273205</v>
+        <v>0.04623057392732049</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01608454376949094</v>
+        <v>0.01608454376949093</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1032269534673559</v>
+        <v>0.1032269534673555</v>
       </c>
       <c r="I4" t="n">
-        <v>4.478749653244515e-06</v>
+        <v>4.478749653244517e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001475968125502382</v>
+        <v>0.001475968125502377</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005118599600839891</v>
+        <v>0.005118599600839435</v>
       </c>
       <c r="L4" t="n">
         <v>1.496498643992295</v>
@@ -2675,31 +2675,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.933188744056502</v>
+        <v>1.933188744056512</v>
       </c>
       <c r="E5" t="n">
         <v>0.3071897010666447</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06189617952202895</v>
+        <v>0.06189617952202886</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633277066395225</v>
+        <v>0.01633277066395223</v>
       </c>
       <c r="H5" t="n">
         <v>0.1026456858813213</v>
       </c>
       <c r="I5" t="n">
-        <v>4.697405856089046e-06</v>
+        <v>4.697405856089048e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001478140944765202</v>
+        <v>0.001478140944765209</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004978680147383142</v>
+        <v>0.004978680147379139</v>
       </c>
       <c r="L5" t="n">
-        <v>1.438662886620088</v>
+        <v>1.43866288662009</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -2720,28 +2720,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.563411899747856</v>
+        <v>1.563411899747855</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2615485786687151</v>
+        <v>0.2615485786687146</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01962166058056866</v>
+        <v>0.01962166058056864</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01555433570026901</v>
+        <v>0.01555433570026903</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09792841485369524</v>
+        <v>0.09792841485369533</v>
       </c>
       <c r="I6" t="n">
-        <v>3.032801083369397e-06</v>
+        <v>3.032801083369398e-06</v>
       </c>
       <c r="J6" t="n">
         <v>0.0009711646613532247</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003295756252631228</v>
+        <v>0.003295756252624918</v>
       </c>
       <c r="L6" t="n">
         <v>1.164488943121784</v>
@@ -2765,31 +2765,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.113455082320917</v>
+        <v>1.113455082320924</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2329019894823983</v>
+        <v>0.232901989482399</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005598149906489806</v>
+        <v>0.005598149906489822</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01522063129562811</v>
+        <v>0.01522063129562813</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09461779863372144</v>
+        <v>0.09461779863372106</v>
       </c>
       <c r="I7" t="n">
-        <v>2.119070448404084e-06</v>
+        <v>2.119070448404089e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0006585951945749482</v>
+        <v>0.0006585951945749529</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002134099585074886</v>
+        <v>0.002134099585073036</v>
       </c>
       <c r="L7" t="n">
-        <v>0.762321696993683</v>
+        <v>0.7623216969936828</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -2813,28 +2813,28 @@
         <v>1.008050356239529</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2199898397917169</v>
+        <v>0.2199898397917166</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001688545244405813</v>
+        <v>0.001688545244405792</v>
       </c>
       <c r="G8" t="n">
         <v>0.01511319463166096</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09389298586570861</v>
+        <v>0.09389298586570859</v>
       </c>
       <c r="I8" t="n">
-        <v>1.891597215245667e-06</v>
+        <v>1.891597215245668e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0005862518242959868</v>
+        <v>0.0005862518242959866</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001881046589807585</v>
+        <v>0.001881046589811332</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6748965984766395</v>
+        <v>0.6748965984766397</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -2855,31 +2855,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.985746320413794</v>
+        <v>1.985746320413793</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2972841052772226</v>
+        <v>0.2972841052772225</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03481360698771365</v>
+        <v>0.03481360698771366</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01588777128700564</v>
+        <v>0.01588777128700575</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1021549687294601</v>
+        <v>0.10215496872946</v>
       </c>
       <c r="I9" t="n">
-        <v>4.083917580542708e-06</v>
+        <v>4.083917580542697e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001354642453770526</v>
+        <v>0.001354642453770521</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004723345409296465</v>
+        <v>0.004723345409295307</v>
       </c>
       <c r="L9" t="n">
-        <v>1.529523779882088</v>
+        <v>1.529523779882081</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -2900,31 +2900,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.446159574316731</v>
+        <v>1.446159574316738</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2640651136865302</v>
+        <v>0.2640651136865299</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01986683114758114</v>
+        <v>0.01986683114758116</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0155419510287164</v>
+        <v>0.01554195102871645</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09771505021014572</v>
+        <v>0.09771505021014575</v>
       </c>
       <c r="I10" t="n">
-        <v>2.971311222180372e-06</v>
+        <v>2.971311222180374e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0009479500521940561</v>
+        <v>0.0009479500521940576</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003189125787302563</v>
+        <v>0.003189125787286522</v>
       </c>
       <c r="L10" t="n">
-        <v>1.044830579047862</v>
+        <v>1.044830579047866</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -2945,31 +2945,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.19844040788766</v>
+        <v>1.198440407887656</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2442859140498659</v>
+        <v>0.2442859140498653</v>
       </c>
       <c r="F11" t="n">
-        <v>0.009536712106717464</v>
+        <v>0.009536712106717414</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01532957183617093</v>
+        <v>0.01532957183617092</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09502922758055185</v>
+        <v>0.09502922758055188</v>
       </c>
       <c r="I11" t="n">
-        <v>2.290823641263544e-06</v>
+        <v>2.290823641263525e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0007023259361067606</v>
+        <v>0.0007023259361067589</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00226487519912579</v>
+        <v>0.002264875199123998</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8312894882605262</v>
+        <v>0.831289488260514</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -3066,31 +3066,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.049296910961288</v>
+        <v>4.049296910961277</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3237534701542786</v>
+        <v>0.323753470154279</v>
       </c>
       <c r="F2" t="n">
         <v>0.05218557395712024</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01622465499368875</v>
+        <v>0.01622465499368885</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1041155420134817</v>
+        <v>0.1041155420134807</v>
       </c>
       <c r="I2" t="n">
-        <v>4.813530845089292e-06</v>
+        <v>4.813530845089288e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001568054437510769</v>
+        <v>0.001568054437510767</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005432732615621398</v>
+        <v>0.005432732615620378</v>
       </c>
       <c r="L2" t="n">
-        <v>3.546012151963009</v>
+        <v>3.546012151963003</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -3111,31 +3111,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.380423133936789</v>
+        <v>3.380423133936787</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3100380369309446</v>
+        <v>0.3100380369309442</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03909404359035792</v>
+        <v>0.03909404359035786</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01599769206182827</v>
+        <v>0.01599769206182814</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1035766291563601</v>
+        <v>0.1035766291563592</v>
       </c>
       <c r="I3" t="n">
-        <v>4.435189261443129e-06</v>
+        <v>4.435189261443128e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00148908769900274</v>
+        <v>0.001489087699002744</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005226794412109219</v>
+        <v>0.005226794412108399</v>
       </c>
       <c r="L3" t="n">
-        <v>2.904996385421448</v>
+        <v>2.90499638542145</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -3156,31 +3156,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.953628205283134</v>
+        <v>2.95362820528313</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3026318292417142</v>
+        <v>0.3026318292417149</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0462305739273205</v>
+        <v>0.04623057392732049</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01608454376949094</v>
+        <v>0.01608454376949093</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1032269534673559</v>
+        <v>0.1032269534673555</v>
       </c>
       <c r="I4" t="n">
-        <v>4.478749653244515e-06</v>
+        <v>4.478749653244517e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001475968125502382</v>
+        <v>0.001475968125502377</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005118599600839891</v>
+        <v>0.005118599600839435</v>
       </c>
       <c r="L4" t="n">
-        <v>2.47885525647173</v>
+        <v>2.478855256471725</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -3201,31 +3201,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.802918107978558</v>
+        <v>2.802918107978555</v>
       </c>
       <c r="E5" t="n">
         <v>0.3071897010666447</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06189617952202895</v>
+        <v>0.06189617952202886</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633277066395225</v>
+        <v>0.01633277066395223</v>
       </c>
       <c r="H5" t="n">
         <v>0.1026456858813213</v>
       </c>
       <c r="I5" t="n">
-        <v>4.697405856089046e-06</v>
+        <v>4.697405856089048e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001478140944765202</v>
+        <v>0.001478140944765209</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004978680147383142</v>
+        <v>0.004978680147379139</v>
       </c>
       <c r="L5" t="n">
-        <v>2.308392250542143</v>
+        <v>2.308392250542141</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -3246,31 +3246,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.350203321174833</v>
+        <v>2.350203321174826</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2615485786687151</v>
+        <v>0.2615485786687146</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01962166058056866</v>
+        <v>0.01962166058056864</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01555433570026901</v>
+        <v>0.01555433570026903</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09792841485369524</v>
+        <v>0.09792841485369533</v>
       </c>
       <c r="I6" t="n">
-        <v>3.032801083369397e-06</v>
+        <v>3.032801083369398e-06</v>
       </c>
       <c r="J6" t="n">
         <v>0.0009711646613532247</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003295756252631228</v>
+        <v>0.003295756252624918</v>
       </c>
       <c r="L6" t="n">
-        <v>1.95128035709092</v>
+        <v>1.951280357090919</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -3291,31 +3291,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.563304944636938</v>
+        <v>1.563304944636937</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2329019894823983</v>
+        <v>0.232901989482399</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005598149906489806</v>
+        <v>0.005598149906489822</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01522063129562811</v>
+        <v>0.01522063129562813</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09461779863372144</v>
+        <v>0.09461779863372106</v>
       </c>
       <c r="I7" t="n">
-        <v>2.119070448404084e-06</v>
+        <v>2.119070448404089e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0006585951945749482</v>
+        <v>0.0006585951945749529</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002134099585074886</v>
+        <v>0.002134099585073036</v>
       </c>
       <c r="L7" t="n">
-        <v>1.212171559309698</v>
+        <v>1.2121715593097</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -3336,31 +3336,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.39777555769607</v>
+        <v>1.397775557696061</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2199898397917169</v>
+        <v>0.2199898397917166</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001688545244405813</v>
+        <v>0.001688545244405792</v>
       </c>
       <c r="G8" t="n">
         <v>0.01511319463166096</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09389298586570861</v>
+        <v>0.09389298586570859</v>
       </c>
       <c r="I8" t="n">
-        <v>1.891597215245667e-06</v>
+        <v>1.891597215245668e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0005862518242959868</v>
+        <v>0.0005862518242959866</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001881046589807585</v>
+        <v>0.001881046589811332</v>
       </c>
       <c r="L8" t="n">
-        <v>1.064621799933171</v>
+        <v>1.06462179993317</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -3381,31 +3381,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.113081347027166</v>
+        <v>3.113081347027162</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2972841052772226</v>
+        <v>0.2972841052772225</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03481360698771365</v>
+        <v>0.03481360698771366</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01588777128700564</v>
+        <v>0.01588777128700575</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1021549687294601</v>
+        <v>0.10215496872946</v>
       </c>
       <c r="I9" t="n">
-        <v>4.083917580542708e-06</v>
+        <v>4.083917580542697e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001354642453770526</v>
+        <v>0.001354642453770521</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004723345409296465</v>
+        <v>0.004723345409295307</v>
       </c>
       <c r="L9" t="n">
-        <v>2.656858795809683</v>
+        <v>2.65685879580968</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -3426,31 +3426,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.075152137764516</v>
+        <v>2.075152137764517</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2640651136865302</v>
+        <v>0.2640651136865299</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01986683114758114</v>
+        <v>0.01986683114758116</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0155419510287164</v>
+        <v>0.01554195102871645</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09771505021014572</v>
+        <v>0.09771505021014575</v>
       </c>
       <c r="I10" t="n">
-        <v>2.971311222180372e-06</v>
+        <v>2.971311222180374e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0009479500521940561</v>
+        <v>0.0009479500521940576</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003189125787302563</v>
+        <v>0.003189125787286522</v>
       </c>
       <c r="L10" t="n">
-        <v>1.673823142495651</v>
+        <v>1.673823142495652</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -3471,28 +3471,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.599177413441611</v>
+        <v>1.599177413441613</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2442859140498659</v>
+        <v>0.2442859140498653</v>
       </c>
       <c r="F11" t="n">
-        <v>0.009536712106717464</v>
+        <v>0.009536712106717414</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01532957183617093</v>
+        <v>0.01532957183617092</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09502922758055185</v>
+        <v>0.09502922758055188</v>
       </c>
       <c r="I11" t="n">
-        <v>2.290823641263544e-06</v>
+        <v>2.290823641263525e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0007023259361067606</v>
+        <v>0.0007023259361067589</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00226487519912579</v>
+        <v>0.002264875199123998</v>
       </c>
       <c r="L11" t="n">
         <v>1.232026493814477</v>
